--- a/r4-core-148-apply-template-for-base-igs/StructureDefinition-at-core-ext-address-municipalityKey.xlsx
+++ b/r4-core-148-apply-template-for-base-igs/StructureDefinition-at-core-ext-address-municipalityKey.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="109">
   <si>
     <t>Property</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Address Municipality Key (Gemeindekennziffer)</t>
+    <t>Address GKZ (Gemeindekennziffer)</t>
   </si>
   <si>
     <t>Status</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T17:40:42+00:00</t>
+    <t>2026-10-20T06:06:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -257,6 +257,12 @@
   <si>
     <t xml:space="preserve">
 </t>
+  </si>
+  <si>
+    <t>Gemeindekennziffer (GKZ)</t>
+  </si>
+  <si>
+    <t>The Gemeindekennziffer (GKZ) of the Austrian municipality the address belongs to, as published by Statistics Austria (Statistik Austria). It is generally identical to the municipality code (Gemeindecode), except in Vienna, where the Gemeindekennziffer is 90001 for the whole city while the Gemeindecode varies by district.</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1
@@ -852,10 +858,10 @@
         <v>80</v>
       </c>
       <c r="L2" t="s" s="2">
-        <v>9</v>
+        <v>81</v>
       </c>
       <c r="M2" t="s" s="2">
-        <v>23</v>
+        <v>82</v>
       </c>
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
@@ -915,10 +921,10 @@
         <v>79</v>
       </c>
       <c r="AI2" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AK2" t="s" s="2">
         <v>21</v>
@@ -926,10 +932,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -940,7 +946,7 @@
         <v>78</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>21</v>
@@ -952,13 +958,13 @@
         <v>21</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
@@ -1009,13 +1015,13 @@
         <v>21</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>21</v>
@@ -1024,15 +1030,15 @@
         <v>21</v>
       </c>
       <c r="AK3" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -1055,13 +1061,13 @@
         <v>21</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="L4" t="s" s="2">
         <v>31</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1100,19 +1106,19 @@
         <v>21</v>
       </c>
       <c r="AB4" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AC4" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AD4" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE4" t="s" s="2">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>78</v>
@@ -1124,7 +1130,7 @@
         <v>21</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>21</v>
@@ -1132,10 +1138,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1143,10 +1149,10 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>21</v>
@@ -1158,16 +1164,16 @@
         <v>21</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -1217,13 +1223,13 @@
         <v>21</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>21</v>
@@ -1232,15 +1238,15 @@
         <v>21</v>
       </c>
       <c r="AK5" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1248,10 +1254,10 @@
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>21</v>
@@ -1263,13 +1269,13 @@
         <v>21</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1320,22 +1326,22 @@
         <v>21</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="AK6" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>
